--- a/source_data/SourceData_EDFig4.xlsx
+++ b/source_data/SourceData_EDFig4.xlsx
@@ -710,7 +710,7 @@
         <v>16641.02922668158</v>
       </c>
       <c r="H5" t="n">
-        <v>15.51555967209343</v>
+        <v>15.5091508671665</v>
       </c>
       <c r="J5" t="n">
         <v>157</v>
@@ -743,7 +743,7 @@
         <v>1920</v>
       </c>
       <c r="H6" t="n">
-        <v>15.5428780802548</v>
+        <v>15.54287801912185</v>
       </c>
       <c r="J6" t="n">
         <v>79</v>
@@ -776,7 +776,7 @@
         <v>12865.33351978744</v>
       </c>
       <c r="H7" t="n">
-        <v>15.68592688820667</v>
+        <v>15.68135157201682</v>
       </c>
       <c r="J7" t="n">
         <v>157</v>
@@ -809,10 +809,10 @@
         <v>604000</v>
       </c>
       <c r="H8" t="n">
-        <v>15.94026296255697</v>
+        <v>15.88075081788533</v>
       </c>
       <c r="I8" t="n">
-        <v>14.8011102438811</v>
+        <v>14.75844177235617</v>
       </c>
       <c r="J8" t="n">
         <v>106</v>
@@ -845,7 +845,7 @@
         <v>144000</v>
       </c>
       <c r="H9" t="n">
-        <v>16.01727564705142</v>
+        <v>16.01706713081194</v>
       </c>
       <c r="J9" t="n">
         <v>154</v>
@@ -878,10 +878,10 @@
         <v>158000</v>
       </c>
       <c r="H10" t="n">
-        <v>16.31299529741685</v>
+        <v>16.29624559873036</v>
       </c>
       <c r="I10" t="n">
-        <v>15.06886674201865</v>
+        <v>15.05550513764555</v>
       </c>
       <c r="J10" t="n">
         <v>116</v>
@@ -914,7 +914,7 @@
         <v>10875</v>
       </c>
       <c r="H11" t="n">
-        <v>16.31700896611387</v>
+        <v>16.31056913453592</v>
       </c>
       <c r="J11" t="n">
         <v>84</v>
@@ -980,10 +980,10 @@
         <v>3125000</v>
       </c>
       <c r="H13" t="n">
-        <v>17.52559198205939</v>
+        <v>17.22165142925473</v>
       </c>
       <c r="I13" t="n">
-        <v>15.59487250081747</v>
+        <v>15.49738797410795</v>
       </c>
       <c r="J13" t="n">
         <v>109</v>
@@ -1016,10 +1016,10 @@
         <v>105000</v>
       </c>
       <c r="H14" t="n">
-        <v>17.82126562995367</v>
+        <v>17.79478561142073</v>
       </c>
       <c r="I14" t="n">
-        <v>15.63295484288588</v>
+        <v>15.62490554740077</v>
       </c>
       <c r="J14" t="n">
         <v>105</v>
@@ -1052,7 +1052,7 @@
         <v>92307.6923076923</v>
       </c>
       <c r="H15" t="n">
-        <v>18.27959353487723</v>
+        <v>18.27631008120813</v>
       </c>
       <c r="J15" t="n">
         <v>199</v>
@@ -1085,7 +1085,7 @@
         <v>566666.6666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>18.9240266858385</v>
+        <v>18.9237857349846</v>
       </c>
       <c r="J16" t="n">
         <v>82</v>
@@ -1118,10 +1118,10 @@
         <v>626000</v>
       </c>
       <c r="H17" t="n">
-        <v>19.26788699200953</v>
+        <v>19.22956838661794</v>
       </c>
       <c r="I17" t="n">
-        <v>16.48682528876611</v>
+        <v>16.46737343743095</v>
       </c>
       <c r="J17" t="n">
         <v>77</v>
@@ -1154,10 +1154,10 @@
         <v>74000</v>
       </c>
       <c r="H18" t="n">
-        <v>19.54280949797445</v>
+        <v>19.52695484553665</v>
       </c>
       <c r="I18" t="n">
-        <v>16.39201830240722</v>
+        <v>16.38224917302435</v>
       </c>
       <c r="J18" t="n">
         <v>105</v>
@@ -1226,7 +1226,7 @@
         <v>1400000</v>
       </c>
       <c r="H20" t="n">
-        <v>19.9401196371148</v>
+        <v>19.93945101197486</v>
       </c>
       <c r="J20" t="n">
         <v>81</v>
@@ -1259,10 +1259,10 @@
         <v>1204000</v>
       </c>
       <c r="H21" t="n">
-        <v>20.21847359340163</v>
+        <v>20.15445709110676</v>
       </c>
       <c r="I21" t="n">
-        <v>17.1860158326566</v>
+        <v>17.11781261270464</v>
       </c>
       <c r="J21" t="n">
         <v>176</v>
@@ -1295,7 +1295,7 @@
         <v>21320</v>
       </c>
       <c r="H22" t="n">
-        <v>20.41840307654648</v>
+        <v>20.41458137591642</v>
       </c>
       <c r="J22" t="n">
         <v>134</v>
@@ -1328,10 +1328,10 @@
         <v>114500</v>
       </c>
       <c r="H23" t="n">
-        <v>20.50315061539488</v>
+        <v>20.49242064997426</v>
       </c>
       <c r="I23" t="n">
-        <v>18.00406486584858</v>
+        <v>17.99470055418258</v>
       </c>
       <c r="J23" t="n">
         <v>96</v>
@@ -1364,10 +1364,10 @@
         <v>188111.1111111111</v>
       </c>
       <c r="H24" t="n">
-        <v>20.60852804622976</v>
+        <v>20.60035403289035</v>
       </c>
       <c r="I24" t="n">
-        <v>18.18708126735275</v>
+        <v>18.17996532532548</v>
       </c>
       <c r="J24" t="n">
         <v>115</v>
@@ -1400,10 +1400,10 @@
         <v>188111.1111111111</v>
       </c>
       <c r="H25" t="n">
-        <v>20.60852804622976</v>
+        <v>20.60035403289035</v>
       </c>
       <c r="I25" t="n">
-        <v>18.18708126735275</v>
+        <v>18.17996532532548</v>
       </c>
       <c r="J25" t="n">
         <v>195</v>
@@ -1436,10 +1436,10 @@
         <v>719032.2580645161</v>
       </c>
       <c r="H26" t="n">
-        <v>20.88392783136021</v>
+        <v>20.78271547037707</v>
       </c>
       <c r="I26" t="n">
-        <v>17.99953686425504</v>
+        <v>17.93177808701002</v>
       </c>
       <c r="J26" t="n">
         <v>177</v>
@@ -1472,7 +1472,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="H27" t="n">
-        <v>21.24285833888526</v>
+        <v>21.2401571660666</v>
       </c>
       <c r="J27" t="n">
         <v>67</v>
@@ -1505,10 +1505,10 @@
         <v>634888.8888888889</v>
       </c>
       <c r="H28" t="n">
-        <v>21.38162772523852</v>
+        <v>21.30442019260907</v>
       </c>
       <c r="I28" t="n">
-        <v>18.1658670688078</v>
+        <v>18.10680560829568</v>
       </c>
       <c r="J28" t="n">
         <v>82</v>
@@ -1541,10 +1541,10 @@
         <v>380000</v>
       </c>
       <c r="H29" t="n">
-        <v>21.48381139023793</v>
+        <v>21.37188136664816</v>
       </c>
       <c r="I29" t="n">
-        <v>18.18074192407538</v>
+        <v>18.09852931446574</v>
       </c>
       <c r="J29" t="n">
         <v>171</v>
@@ -1577,10 +1577,10 @@
         <v>73913.04347826086</v>
       </c>
       <c r="H30" t="n">
-        <v>21.52751642022882</v>
+        <v>21.52722858354669</v>
       </c>
       <c r="I30" t="n">
-        <v>18.22614320114317</v>
+        <v>18.22593428354077</v>
       </c>
       <c r="J30" t="n">
         <v>168</v>
@@ -1613,10 +1613,10 @@
         <v>81000</v>
       </c>
       <c r="H31" t="n">
-        <v>21.62045387520759</v>
+        <v>21.62004243546474</v>
       </c>
       <c r="I31" t="n">
-        <v>18.39789791214488</v>
+        <v>18.39761294088624</v>
       </c>
       <c r="J31" t="n">
         <v>169</v>
@@ -1649,10 +1649,10 @@
         <v>24038.46153846154</v>
       </c>
       <c r="H32" t="n">
-        <v>21.62982995673705</v>
+        <v>21.63012599814882</v>
       </c>
       <c r="I32" t="n">
-        <v>18.48106926843412</v>
+        <v>18.48118443757064</v>
       </c>
       <c r="J32" t="n">
         <v>117</v>
@@ -1685,10 +1685,10 @@
         <v>104000</v>
       </c>
       <c r="H33" t="n">
-        <v>21.64565328468139</v>
+        <v>21.64527485456869</v>
       </c>
       <c r="I33" t="n">
-        <v>18.41532748510019</v>
+        <v>18.41506608586634</v>
       </c>
       <c r="J33" t="n">
         <v>170</v>
@@ -1721,10 +1721,10 @@
         <v>2210833.333333333</v>
       </c>
       <c r="H34" t="n">
-        <v>21.72650615311951</v>
+        <v>21.76221947626512</v>
       </c>
       <c r="I34" t="n">
-        <v>18.8106786913261</v>
+        <v>18.8149928148991</v>
       </c>
       <c r="J34" t="n">
         <v>187</v>
@@ -1757,10 +1757,10 @@
         <v>38500</v>
       </c>
       <c r="H35" t="n">
-        <v>21.78946668425935</v>
+        <v>21.78930735776838</v>
       </c>
       <c r="I35" t="n">
-        <v>18.98122294877135</v>
+        <v>18.98098696378628</v>
       </c>
       <c r="J35" t="n">
         <v>167</v>
@@ -1793,10 +1793,10 @@
         <v>486000</v>
       </c>
       <c r="H36" t="n">
-        <v>21.92189577089803</v>
+        <v>21.92174435531882</v>
       </c>
       <c r="I36" t="n">
-        <v>19.29087967405975</v>
+        <v>19.29062764485845</v>
       </c>
       <c r="J36" t="n">
         <v>172</v>
@@ -1829,10 +1829,10 @@
         <v>144340</v>
       </c>
       <c r="H37" t="n">
-        <v>21.98558294896831</v>
+        <v>21.98536682360781</v>
       </c>
       <c r="I37" t="n">
-        <v>19.0056192911464</v>
+        <v>19.00547571699945</v>
       </c>
       <c r="J37" t="n">
         <v>175</v>
@@ -1865,10 +1865,10 @@
         <v>112220</v>
       </c>
       <c r="H38" t="n">
-        <v>22.10531417136249</v>
+        <v>22.10515879556368</v>
       </c>
       <c r="I38" t="n">
-        <v>19.08388631958708</v>
+        <v>19.08378650055852</v>
       </c>
       <c r="J38" t="n">
         <v>174</v>
@@ -1901,10 +1901,10 @@
         <v>95750</v>
       </c>
       <c r="H39" t="n">
-        <v>22.18403759214089</v>
+        <v>22.18328192693386</v>
       </c>
       <c r="I39" t="n">
-        <v>19.28895266215994</v>
+        <v>19.28841919428085</v>
       </c>
       <c r="J39" t="n">
         <v>178</v>
@@ -1937,10 +1937,10 @@
         <v>4146666.666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>22.21762548777048</v>
+        <v>22.21693002558449</v>
       </c>
       <c r="I40" t="n">
-        <v>19.22613184874692</v>
+        <v>19.22566949948449</v>
       </c>
       <c r="J40" t="n">
         <v>190</v>
@@ -1973,10 +1973,10 @@
         <v>44480</v>
       </c>
       <c r="H41" t="n">
-        <v>22.24627089066778</v>
+        <v>22.23441804576935</v>
       </c>
       <c r="I41" t="n">
-        <v>18.39628638204979</v>
+        <v>18.38651705441137</v>
       </c>
       <c r="J41" t="n">
         <v>118</v>
@@ -2009,10 +2009,10 @@
         <v>1280000</v>
       </c>
       <c r="H42" t="n">
-        <v>22.30228578978384</v>
+        <v>22.26949764505553</v>
       </c>
       <c r="I42" t="n">
-        <v>19.73825180439047</v>
+        <v>19.71360341245012</v>
       </c>
       <c r="J42" t="n">
         <v>185</v>
@@ -2045,10 +2045,10 @@
         <v>342741.935483871</v>
       </c>
       <c r="H43" t="n">
-        <v>22.34666271419135</v>
+        <v>22.34629490641281</v>
       </c>
       <c r="I43" t="n">
-        <v>19.77671963556965</v>
+        <v>19.77644633535914</v>
       </c>
       <c r="J43" t="n">
         <v>101</v>
@@ -2081,10 +2081,10 @@
         <v>464250</v>
       </c>
       <c r="H44" t="n">
-        <v>22.40254117691718</v>
+        <v>22.401891205133</v>
       </c>
       <c r="I44" t="n">
-        <v>19.41929477239402</v>
+        <v>19.41897404157888</v>
       </c>
       <c r="J44" t="n">
         <v>180</v>
@@ -2117,10 +2117,10 @@
         <v>24000</v>
       </c>
       <c r="H45" t="n">
-        <v>22.4243867839569</v>
+        <v>22.42438620103372</v>
       </c>
       <c r="I45" t="n">
-        <v>20.26838805456152</v>
+        <v>20.2683867945907</v>
       </c>
       <c r="J45" t="n">
         <v>165</v>
@@ -2153,10 +2153,10 @@
         <v>5782608.695652174</v>
       </c>
       <c r="H46" t="n">
-        <v>22.43848613153626</v>
+        <v>22.43766932192126</v>
       </c>
       <c r="I46" t="n">
-        <v>19.9012117027526</v>
+        <v>19.90059826136212</v>
       </c>
       <c r="J46" t="n">
         <v>192</v>
@@ -2165,70 +2165,70 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3.4 wt% Co–N–C</t>
+          <t>Ru/Pr2O3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.73</v>
+        <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>4340</v>
+        <v>64000</v>
       </c>
       <c r="G47" t="n">
-        <v>116353.8873994638</v>
+        <v>1280000</v>
       </c>
       <c r="H47" t="n">
-        <v>22.54484973796892</v>
+        <v>22.50875227002852</v>
+      </c>
+      <c r="I47" t="n">
+        <v>19.11011498891022</v>
       </c>
       <c r="J47" t="n">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ru/Pr2O3</t>
+          <t>3.4 wt% Co–N–C</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>3.73</v>
       </c>
       <c r="D48" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>64000</v>
+        <v>4340</v>
       </c>
       <c r="G48" t="n">
-        <v>1280000</v>
+        <v>116353.8873994638</v>
       </c>
       <c r="H48" t="n">
-        <v>22.58696610857199</v>
-      </c>
-      <c r="I48" t="n">
-        <v>19.18608642663893</v>
+        <v>22.54368102061514</v>
       </c>
       <c r="J48" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49">
@@ -2258,10 +2258,10 @@
         <v>2240000</v>
       </c>
       <c r="H49" t="n">
-        <v>22.60674725199266</v>
+        <v>22.58972546066001</v>
       </c>
       <c r="I49" t="n">
-        <v>20.53557117927961</v>
+        <v>20.51610109982357</v>
       </c>
       <c r="J49" t="n">
         <v>184</v>
@@ -2294,10 +2294,10 @@
         <v>1080000</v>
       </c>
       <c r="H50" t="n">
-        <v>22.66155427079388</v>
+        <v>22.63422190250466</v>
       </c>
       <c r="I50" t="n">
-        <v>19.99958887695469</v>
+        <v>19.97839032758582</v>
       </c>
       <c r="J50" t="n">
         <v>186</v>
@@ -2330,10 +2330,10 @@
         <v>152500</v>
       </c>
       <c r="H51" t="n">
-        <v>22.73773953945267</v>
+        <v>22.73911866181321</v>
       </c>
       <c r="I51" t="n">
-        <v>20.06228377893208</v>
+        <v>20.06350601417598</v>
       </c>
       <c r="J51" t="n">
         <v>162</v>
@@ -2366,10 +2366,10 @@
         <v>2106666.666666667</v>
       </c>
       <c r="H52" t="n">
-        <v>22.79787449624272</v>
+        <v>22.79707615469821</v>
       </c>
       <c r="I52" t="n">
-        <v>19.67159306583043</v>
+        <v>19.67121736144116</v>
       </c>
       <c r="J52" t="n">
         <v>191</v>
@@ -2402,10 +2402,10 @@
         <v>3279069.76744186</v>
       </c>
       <c r="H53" t="n">
-        <v>22.97770863250099</v>
+        <v>22.97505023442373</v>
       </c>
       <c r="I53" t="n">
-        <v>21.14159159296535</v>
+        <v>21.13842463633245</v>
       </c>
       <c r="J53" t="n">
         <v>81</v>
@@ -2438,7 +2438,7 @@
         <v>67.22689075630252</v>
       </c>
       <c r="H54" t="n">
-        <v>23.08299364512096</v>
+        <v>23.08299349565035</v>
       </c>
       <c r="J54" t="n">
         <v>76</v>
@@ -2471,10 +2471,10 @@
         <v>215000</v>
       </c>
       <c r="H55" t="n">
-        <v>23.20513240513247</v>
+        <v>23.20436073707794</v>
       </c>
       <c r="I55" t="n">
-        <v>20.12113185576782</v>
+        <v>20.12072416313562</v>
       </c>
       <c r="J55" t="n">
         <v>181</v>
@@ -2507,10 +2507,10 @@
         <v>181500</v>
       </c>
       <c r="H56" t="n">
-        <v>23.21754723436856</v>
+        <v>23.22687763512296</v>
       </c>
       <c r="I56" t="n">
-        <v>20.46191590280913</v>
+        <v>20.46935647932307</v>
       </c>
       <c r="J56" t="n">
         <v>164</v>
@@ -2543,10 +2543,10 @@
         <v>32225</v>
       </c>
       <c r="H57" t="n">
-        <v>23.22789996923463</v>
+        <v>23.22776998802789</v>
       </c>
       <c r="I57" t="n">
-        <v>19.81693600574157</v>
+        <v>19.81687091043289</v>
       </c>
       <c r="J57" t="n">
         <v>178</v>
@@ -2579,10 +2579,10 @@
         <v>210000</v>
       </c>
       <c r="H58" t="n">
-        <v>23.30663036319694</v>
+        <v>23.30580558092457</v>
       </c>
       <c r="I58" t="n">
-        <v>20.68915510023711</v>
+        <v>20.68866835664272</v>
       </c>
       <c r="J58" t="n">
         <v>179</v>
@@ -2615,10 +2615,10 @@
         <v>391750</v>
       </c>
       <c r="H59" t="n">
-        <v>23.32994138420145</v>
+        <v>23.32917066895267</v>
       </c>
       <c r="I59" t="n">
-        <v>19.86733676694525</v>
+        <v>19.86696646925644</v>
       </c>
       <c r="J59" t="n">
         <v>94</v>
@@ -2651,10 +2651,10 @@
         <v>418701.2987012987</v>
       </c>
       <c r="H60" t="n">
-        <v>23.3806887186201</v>
+        <v>23.37988813206525</v>
       </c>
       <c r="I60" t="n">
-        <v>19.93166290933067</v>
+        <v>19.93127182313833</v>
       </c>
       <c r="J60" t="n">
         <v>183</v>
@@ -2687,10 +2687,10 @@
         <v>382383.4196891192</v>
       </c>
       <c r="H61" t="n">
-        <v>23.49981359461895</v>
+        <v>23.49895488665815</v>
       </c>
       <c r="I61" t="n">
-        <v>19.98685282787688</v>
+        <v>19.98643144807416</v>
       </c>
       <c r="J61" t="n">
         <v>183</v>
@@ -2723,10 +2723,10 @@
         <v>960000</v>
       </c>
       <c r="H62" t="n">
-        <v>23.54534376164739</v>
+        <v>23.51767409881526</v>
       </c>
       <c r="I62" t="n">
-        <v>20.52873756182436</v>
+        <v>20.51356024600929</v>
       </c>
       <c r="J62" t="n">
         <v>188</v>
@@ -2759,7 +2759,7 @@
         <v>240</v>
       </c>
       <c r="H63" t="n">
-        <v>23.71054962146314</v>
+        <v>23.71054935914687</v>
       </c>
       <c r="J63" t="n">
         <v>79</v>
@@ -2792,10 +2792,10 @@
         <v>1410000</v>
       </c>
       <c r="H64" t="n">
-        <v>23.71111091493324</v>
+        <v>23.7109326477648</v>
       </c>
       <c r="I64" t="n">
-        <v>22.46339128522992</v>
+        <v>22.4632665502814</v>
       </c>
       <c r="J64" t="n">
         <v>173</v>
@@ -2828,7 +2828,7 @@
         <v>860000</v>
       </c>
       <c r="H65" t="n">
-        <v>23.7370653751148</v>
+        <v>23.73387896628061</v>
       </c>
       <c r="J65" t="n">
         <v>206</v>
@@ -2861,7 +2861,7 @@
         <v>16400</v>
       </c>
       <c r="H66" t="n">
-        <v>24.08428688319593</v>
+        <v>24.08394547182962</v>
       </c>
       <c r="J66" t="n">
         <v>134</v>
@@ -2894,10 +2894,10 @@
         <v>184750</v>
       </c>
       <c r="H67" t="n">
-        <v>24.4107382267625</v>
+        <v>24.41007009522229</v>
       </c>
       <c r="I67" t="n">
-        <v>20.40037538048987</v>
+        <v>20.39998074223815</v>
       </c>
       <c r="J67" t="n">
         <v>94</v>
@@ -2930,10 +2930,10 @@
         <v>200000</v>
       </c>
       <c r="H68" t="n">
-        <v>24.71430488603433</v>
+        <v>24.80386642961499</v>
       </c>
       <c r="I68" t="n">
-        <v>21.66668781140656</v>
+        <v>21.73392142828638</v>
       </c>
       <c r="J68" t="n">
         <v>164</v>
@@ -2966,10 +2966,10 @@
         <v>3235294.117647059</v>
       </c>
       <c r="H69" t="n">
-        <v>24.90675306015482</v>
+        <v>24.9059971986012</v>
       </c>
       <c r="I69" t="n">
-        <v>20.89006273912438</v>
+        <v>20.88959536260946</v>
       </c>
       <c r="J69" t="n">
         <v>194</v>
@@ -2978,70 +2978,70 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ru/C12A7 (microcube)</t>
+          <t>NI/CeN NPs</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Ni</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>5</v>
+        <v>11.7</v>
       </c>
       <c r="D70" t="n">
         <v>400</v>
       </c>
       <c r="E70" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="F70" t="n">
-        <v>5380</v>
+        <v>6500</v>
       </c>
       <c r="G70" t="n">
-        <v>107600</v>
+        <v>55555.55555555556</v>
       </c>
       <c r="H70" t="n">
-        <v>25.45190220769257</v>
-      </c>
-      <c r="I70" t="n">
-        <v>21.4021461193574</v>
+        <v>25.9193907089895</v>
       </c>
       <c r="J70" t="n">
-        <v>196</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NI/CeN NPs</t>
+          <t>Ru/C12A7 (microcube)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ni</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11.7</v>
+        <v>5</v>
       </c>
       <c r="D71" t="n">
         <v>400</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="F71" t="n">
-        <v>6500</v>
+        <v>5380</v>
       </c>
       <c r="G71" t="n">
-        <v>55555.55555555556</v>
+        <v>107600</v>
       </c>
       <c r="H71" t="n">
-        <v>25.92523059474333</v>
+        <v>26.20136441171531</v>
+      </c>
+      <c r="I71" t="n">
+        <v>21.9371504230411</v>
       </c>
       <c r="J71" t="n">
-        <v>150</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72">
@@ -3071,10 +3071,10 @@
         <v>514629.6296296296</v>
       </c>
       <c r="H72" t="n">
-        <v>26.72546206061724</v>
+        <v>26.717317081552</v>
       </c>
       <c r="I72" t="n">
-        <v>25.12452229978249</v>
+        <v>25.11588950800139</v>
       </c>
       <c r="J72" t="n">
         <v>163</v>
@@ -3083,70 +3083,70 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6 wt% Co/CeO2</t>
+          <t>Ru/CeO2-r</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Co</t>
+          <t>Ru</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D73" t="n">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="E73" t="n">
         <v>10</v>
       </c>
       <c r="F73" t="n">
-        <v>26654</v>
+        <v>115000</v>
       </c>
       <c r="G73" t="n">
-        <v>444233.3333333334</v>
+        <v>1150000</v>
       </c>
       <c r="H73" t="n">
-        <v>28.15030177609778</v>
+        <v>28.11549732185807</v>
+      </c>
+      <c r="I73" t="n">
+        <v>22.80727609747251</v>
       </c>
       <c r="J73" t="n">
-        <v>205</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ru/CeO2-r</t>
+          <t>6 wt% Co/CeO2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ru</t>
+          <t>Co</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="E74" t="n">
         <v>10</v>
       </c>
       <c r="F74" t="n">
-        <v>115000</v>
+        <v>26654</v>
       </c>
       <c r="G74" t="n">
-        <v>1150000</v>
+        <v>444233.3333333334</v>
       </c>
       <c r="H74" t="n">
-        <v>28.16239364178105</v>
-      </c>
-      <c r="I74" t="n">
-        <v>22.83375809565127</v>
+        <v>28.14354075398602</v>
       </c>
       <c r="J74" t="n">
-        <v>100</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75">
@@ -3176,7 +3176,7 @@
         <v>67846.15384615384</v>
       </c>
       <c r="H75" t="n">
-        <v>35.15353985646534</v>
+        <v>35.13257848346144</v>
       </c>
       <c r="J75" t="n">
         <v>197</v>
@@ -3209,10 +3209,10 @@
         <v>9750</v>
       </c>
       <c r="H76" t="n">
-        <v>41.27808885912891</v>
+        <v>41.27598549929062</v>
       </c>
       <c r="I76" t="n">
-        <v>30.31078449179117</v>
+        <v>30.30968171443131</v>
       </c>
       <c r="J76" t="n">
         <v>94</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>17.52559198205939</v>
+        <v>17.22165142925473</v>
       </c>
     </row>
     <row r="85">
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.1443268610664097</v>
+        <v>0.1244811783015827</v>
       </c>
     </row>
     <row r="88">
@@ -3315,7 +3315,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.1562871203122349</v>
+        <v>0.1582000215972726</v>
       </c>
     </row>
   </sheetData>
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15.51555967209343</v>
+        <v>15.5091508671665</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.27959353487723</v>
+        <v>18.27631008120813</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.41840307654648</v>
+        <v>20.41458137591642</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>

--- a/source_data/SourceData_EDFig4.xlsx
+++ b/source_data/SourceData_EDFig4.xlsx
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>881.8</v>
+        <v>881.3</v>
       </c>
       <c r="E5" t="n">
         <v>871.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1.216712580348944</v>
+        <v>1.15932047750229</v>
       </c>
     </row>
     <row r="6">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>873.5</v>
+        <v>873</v>
       </c>
       <c r="E6" t="n">
         <v>871.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2640036730945816</v>
+        <v>0.2066115702479276</v>
       </c>
     </row>
     <row r="7">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>923.8</v>
+        <v>921.6</v>
       </c>
       <c r="E12" t="n">
         <v>1028</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.13618677042802</v>
+        <v>-10.35019455252918</v>
       </c>
     </row>
     <row r="13">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>299</v>
+        <v>298.9</v>
       </c>
       <c r="E13" t="n">
         <v>254</v>
       </c>
       <c r="F13" t="n">
-        <v>17.71653543307086</v>
+        <v>17.6771653543307</v>
       </c>
     </row>
     <row r="14">
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>735.6</v>
+        <v>735.3</v>
       </c>
       <c r="E14" t="n">
         <v>691</v>
       </c>
       <c r="F14" t="n">
-        <v>6.454413892908839</v>
+        <v>6.410998552821989</v>
       </c>
     </row>
     <row r="15">
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>965.9</v>
+        <v>965.6</v>
       </c>
       <c r="E15" t="n">
         <v>921</v>
       </c>
       <c r="F15" t="n">
-        <v>4.875135722041257</v>
+        <v>4.842562432138986</v>
       </c>
     </row>
   </sheetData>
@@ -1453,20 +1453,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>combined_primary_cat1y_dp4.2_recycle10</t>
+          <t>catalyst_repl_95.24EURkg_1y</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2333687232337815</v>
+        <v>0.009669496678287742</v>
       </c>
     </row>
     <row r="5">
@@ -1475,20 +1475,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>combined_primary_cat4y_dp4.2_recycle10</t>
+          <t>combined_primary_cat1y_dp4.2_recycle10</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1966449733212746</v>
+        <v>0.02596540358780233</v>
       </c>
     </row>
     <row r="6">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>recycle_weight_nyari</t>
+          <t>catalyst_repl_95.24EURkg_4y</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2231532873259957</v>
+        <v>0.01092175522218538</v>
       </c>
     </row>
     <row r="7">
@@ -1519,20 +1519,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_1y</t>
+          <t>catalyst_repl_95.24EURkg_6y</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3376088702102948</v>
+        <v>0.01335836382050425</v>
       </c>
     </row>
     <row r="8">
@@ -1541,20 +1541,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75_recycle2.68</t>
+          <t>catalyst_repl_18.1EURkg_3y</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2868523498031414</v>
+        <v>0.01942936471943555</v>
       </c>
     </row>
     <row r="9">
@@ -1563,20 +1563,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75_h2half</t>
+          <t>catalyst_repl_18.1EURkg_5y</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3052838843237611</v>
+        <v>0.02024372852261692</v>
       </c>
     </row>
     <row r="10">
@@ -1585,20 +1585,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>catalyst_repl_18.1EURkg_3y</t>
+          <t>h2_price_half</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E10" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3562480953799437</v>
+        <v>0.02034744778672221</v>
       </c>
     </row>
     <row r="11">
@@ -1607,20 +1607,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>catalyst_repl_18.1EURkg_5y</t>
+          <t>combined_cat3y_dp3.75_h2half</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3571340601230061</v>
+        <v>0.01534154656513514</v>
       </c>
     </row>
     <row r="12">
@@ -1629,20 +1629,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>h2_price_half</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3312334155723725</v>
+        <v>0.01994624397744177</v>
       </c>
     </row>
     <row r="13">
@@ -1651,20 +1651,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>perez_fortes_prices</t>
+          <t>loop_dp_3.75bar</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D13" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3498473699884074</v>
+        <v>0.02267685646679655</v>
       </c>
     </row>
     <row r="14">
@@ -1673,20 +1673,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>recycle_flow_x2.68</t>
+          <t>perez_fortes_prices</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3270474900765253</v>
+        <v>0.01983592942922505</v>
       </c>
     </row>
     <row r="15">
@@ -1695,20 +1695,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_4y</t>
+          <t>recycle_flow_x2.68</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3500709824471828</v>
+        <v>0.02455592957931308</v>
       </c>
     </row>
     <row r="16">
@@ -1717,20 +1717,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_6y</t>
+          <t>loop_dp_4.2bar</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3541493836095832</v>
+        <v>0.02323202226219604</v>
       </c>
     </row>
     <row r="17">
@@ -1739,20 +1739,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>loop_dp_4.2bar</t>
+          <t>ec_split_campos_SI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3303256739439167</v>
+        <v>0.02023780061220415</v>
       </c>
     </row>
     <row r="18">
@@ -1761,20 +1761,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75</t>
+          <t>combined_primary_cat4y_dp4.2_recycle10</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3333426344061412</v>
+        <v>0.03473429724549387</v>
       </c>
     </row>
     <row r="19">
@@ -1783,20 +1783,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>combined_cat3y_dp3.75</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3583691520442965</v>
+        <v>0.02162755544839435</v>
       </c>
     </row>
     <row r="20">
@@ -1805,20 +1805,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>loop_dp_3.75bar</t>
+          <t>combined_cat3y_dp3.75_recycle2.68</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3280425677479598</v>
+        <v>0.02817767246330193</v>
       </c>
     </row>
     <row r="21">
@@ -1827,20 +1827,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ec_split_campos_SI</t>
+          <t>recycle_weight_nyari</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3565569267074893</v>
+        <v>0.05051027627933849</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig4.xlsx
+++ b/source_data/SourceData_EDFig4.xlsx
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>881.3</v>
+        <v>881.8</v>
       </c>
       <c r="E5" t="n">
         <v>871.2</v>
       </c>
       <c r="F5" t="n">
-        <v>1.15932047750229</v>
+        <v>1.216712580348944</v>
       </c>
     </row>
     <row r="6">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>873</v>
+        <v>873.5</v>
       </c>
       <c r="E6" t="n">
         <v>871.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2066115702479276</v>
+        <v>0.2640036730945816</v>
       </c>
     </row>
     <row r="7">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>921.6</v>
+        <v>923.8</v>
       </c>
       <c r="E12" t="n">
         <v>1028</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.35019455252918</v>
+        <v>-10.13618677042802</v>
       </c>
     </row>
     <row r="13">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>298.9</v>
+        <v>299</v>
       </c>
       <c r="E13" t="n">
         <v>254</v>
       </c>
       <c r="F13" t="n">
-        <v>17.6771653543307</v>
+        <v>17.71653543307086</v>
       </c>
     </row>
     <row r="14">
@@ -1160,13 +1160,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>735.3</v>
+        <v>735.6</v>
       </c>
       <c r="E14" t="n">
         <v>691</v>
       </c>
       <c r="F14" t="n">
-        <v>6.410998552821989</v>
+        <v>6.454413892908839</v>
       </c>
     </row>
     <row r="15">
@@ -1186,13 +1186,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>965.6</v>
+        <v>965.9</v>
       </c>
       <c r="E15" t="n">
         <v>921</v>
       </c>
       <c r="F15" t="n">
-        <v>4.842562432138986</v>
+        <v>4.875135722041257</v>
       </c>
     </row>
   </sheetData>
@@ -1453,20 +1453,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_1y</t>
+          <t>combined_primary_cat1y_dp4.2_recycle10</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D4" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009669496678287742</v>
+        <v>0.2333687232337815</v>
       </c>
     </row>
     <row r="5">
@@ -1475,20 +1475,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>combined_primary_cat1y_dp4.2_recycle10</t>
+          <t>combined_primary_cat4y_dp4.2_recycle10</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02596540358780233</v>
+        <v>0.1966449733212746</v>
       </c>
     </row>
     <row r="6">
@@ -1497,20 +1497,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_4y</t>
+          <t>recycle_weight_nyari</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01092175522218538</v>
+        <v>0.2231532873259957</v>
       </c>
     </row>
     <row r="7">
@@ -1519,20 +1519,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_6y</t>
+          <t>catalyst_repl_95.24EURkg_1y</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01335836382050425</v>
+        <v>0.3376088702102948</v>
       </c>
     </row>
     <row r="8">
@@ -1541,20 +1541,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>catalyst_repl_18.1EURkg_3y</t>
+          <t>combined_cat3y_dp3.75_recycle2.68</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01942936471943555</v>
+        <v>0.2868523498031414</v>
       </c>
     </row>
     <row r="9">
@@ -1563,20 +1563,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>catalyst_repl_18.1EURkg_5y</t>
+          <t>combined_cat3y_dp3.75_h2half</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02024372852261692</v>
+        <v>0.3052838843237611</v>
       </c>
     </row>
     <row r="10">
@@ -1585,20 +1585,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>h2_price_half</t>
+          <t>catalyst_repl_18.1EURkg_3y</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D10" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02034744778672221</v>
+        <v>0.3562480953799437</v>
       </c>
     </row>
     <row r="11">
@@ -1607,20 +1607,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75_h2half</t>
+          <t>catalyst_repl_18.1EURkg_5y</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>0.01534154656513514</v>
+        <v>0.3571340601230061</v>
       </c>
     </row>
     <row r="12">
@@ -1629,20 +1629,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>h2_price_half</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01994624397744177</v>
+        <v>0.3312334155723725</v>
       </c>
     </row>
     <row r="13">
@@ -1651,20 +1651,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>loop_dp_3.75bar</t>
+          <t>perez_fortes_prices</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02267685646679655</v>
+        <v>0.3498473699884074</v>
       </c>
     </row>
     <row r="14">
@@ -1673,20 +1673,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>perez_fortes_prices</t>
+          <t>recycle_flow_x2.68</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
-        <v>0.01983592942922505</v>
+        <v>0.3270474900765253</v>
       </c>
     </row>
     <row r="15">
@@ -1695,20 +1695,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>recycle_flow_x2.68</t>
+          <t>catalyst_repl_95.24EURkg_4y</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02455592957931308</v>
+        <v>0.3500709824471828</v>
       </c>
     </row>
     <row r="16">
@@ -1717,20 +1717,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>loop_dp_4.2bar</t>
+          <t>catalyst_repl_95.24EURkg_6y</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>0.02323202226219604</v>
+        <v>0.3541493836095832</v>
       </c>
     </row>
     <row r="17">
@@ -1739,20 +1739,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ec_split_campos_SI</t>
+          <t>loop_dp_4.2bar</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02023780061220415</v>
+        <v>0.3303256739439167</v>
       </c>
     </row>
     <row r="18">
@@ -1761,20 +1761,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>combined_primary_cat4y_dp4.2_recycle10</t>
+          <t>combined_cat3y_dp3.75</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03473429724549387</v>
+        <v>0.3333426344061412</v>
       </c>
     </row>
     <row r="19">
@@ -1783,20 +1783,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02162755544839435</v>
+        <v>0.3583691520442965</v>
       </c>
     </row>
     <row r="20">
@@ -1805,20 +1805,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75_recycle2.68</t>
+          <t>loop_dp_3.75bar</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>0.02817767246330193</v>
+        <v>0.3280425677479598</v>
       </c>
     </row>
     <row r="21">
@@ -1827,20 +1827,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>recycle_weight_nyari</t>
+          <t>ec_split_campos_SI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D21" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05051027627933849</v>
+        <v>0.3565569267074893</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig4.xlsx
+++ b/source_data/SourceData_EDFig4.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>analysis/meoh_plant_benchmark_2026_10_06/reconciliation_cost.csv (case B3 Perez-Fortes 2016)</t>
+          <t>analysis/meoh_plant_benchmark_2026_10_06/reconciliation_cost.csv (case B3 Perez-Fortes 2016), split by analysis/review_pf_benchmark_2026_10_09/pf_benchmark_audit.py</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -487,17 +487,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>panel b</t>
+          <t>constants drawn on panel a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>analysis/meoh_plant_benchmark_2026_10_06/reconciliation_cost.csv (TOTAL and like-for-like rows)</t>
+          <t>analysis/meoh_plant_benchmark_2026_10_06/reconciliation_cost.csv</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -505,17 +505,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>panel c</t>
+          <t>panel b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>analysis/meoh_plant_benchmark_2026_10_06/summary.json (model_cases M7) and reference_values.csv (ref_id PEREZFORTES16)</t>
+          <t>analysis/meoh_plant_benchmark_2026_10_06/reconciliation_cost.csv (TOTAL and like-for-like rows)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -523,20 +523,56 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>panel c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>analysis/meoh_plant_benchmark_2026_10_06/summary.json (model_cases M7) and reference_values.csv (ref_id PEREZFORTES16)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>d</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>panel d</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>analysis/meoh_plant_benchmark_2026_10_06/sensitivity_summary.json (variants)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>constants drawn on panel d</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>analysis/meoh_plant_benchmark_2026_10_06/sensitivity_summary.json</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -549,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -593,7 +629,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_plant_benchmark_2026_10_06/reconciliation_cost.csv (case B3 Perez-Fortes 2016)</t>
+          <t>source: analysis/meoh_plant_benchmark_2026_10_06/reconciliation_cost.csv (case B3 Perez-Fortes 2016), split by analysis/review_pf_benchmark_2026_10_09/pf_benchmark_audit.py</t>
         </is>
       </c>
     </row>
@@ -605,190 +641,258 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>deviation</t>
-        </is>
-      </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>ref_basis</t>
+          <t>deviation_pct</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>613.6</v>
+          <t>stoichiometric H$_2$ and CO$_2$ (3:1)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>catalyst-independent</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>615.7</v>
+        <v>583.2123228801324</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.137</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>raw materials 95.9 % of VCP 283 M EUR/a</t>
-        </is>
+        <v>583.2123228801324</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>electricity + utilities</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>20.23</v>
+          <t>H$_2$ and CO$_2$ above stoichiometry</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>catalyst-sensitive</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>16.69</v>
+        <v>30.34267711986752</v>
       </c>
       <c r="D5" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>utilities 2.6 % of VCP (net power)</t>
-        </is>
+        <v>32.48767711986761</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-6.60250344179989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>catalyst replacement</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9.615</v>
+          <t>electricity (model: compressors; ref.: utilities net)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>catalyst-sensitive</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>9.630000000000001</v>
+        <v>20.23</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01547</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>consumables 1.5 % of VCP</t>
-        </is>
+        <v>16.69</v>
+      </c>
+      <c r="E6" t="n">
+        <v>21.21030557219892</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>capital (annuity at 8 %, 20 y)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>38.14</v>
+          <t>catalyst replacement</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>catalyst-sensitive</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>57.55</v>
+        <v>9.615</v>
       </c>
       <c r="D7" t="n">
-        <v>-19.41</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>breakeven 723.6 minus VCP + FCP 666.05</t>
-        </is>
+        <v>9.630000000000001</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.155763239875395</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fixed O&amp;M</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>33.64</v>
+          <t>capital (8 %, 20 y)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>catalyst-sensitive</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>24.57</v>
+        <v>38.14</v>
       </c>
       <c r="D8" t="n">
-        <v>9.069000000000001</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>FCP 24.57</t>
-        </is>
+        <v>57.55</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-33.72719374456994</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>residual direct + 10 % of NPC (anchor convention)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>126.2</v>
+          <t>fixed O&amp;M (reference value on both sides)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>accounting</t>
+        </is>
       </c>
       <c r="C9" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="D9" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>126.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>no such terms in the reference</t>
-        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TOTAL, like-for-like (feed + power + catalyst + capital + reference FCP)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>706.1</v>
+          <t>catalyst-sensitive subtotal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>subtotal</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>723.6</v>
+        <v>98.32767711986753</v>
       </c>
       <c r="D10" t="n">
-        <v>-17.49</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Table 5</t>
-        </is>
+        <v>116.3576771198676</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-15.49532480046522</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TOTAL, anchor convention</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>841.4</v>
+          <t>total (harmonized; ref.: NPV = 0 break-even price)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
       </c>
       <c r="C11" t="n">
+        <v>706.11</v>
+      </c>
+      <c r="D11" t="n">
         <v>723.6</v>
       </c>
-      <c r="D11" t="n">
-        <v>117.8</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>NPV = 0 breakeven price (Table 5)</t>
+      <c r="E11" t="n">
+        <v>-2.41708126036484</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>constants drawn on panel a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_plant_benchmark_2026_10_06/reconciliation_cost.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>reference_terms_sum</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>724.1400000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>model_own_fixed_om</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>33.64</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>anchor_residual</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>126.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>breakeven_basis</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Table 5</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1446,6 +1550,11 @@
           <t>regret_median_mismatched</t>
         </is>
       </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>knobs</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1453,20 +1562,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>combined_primary_cat1y_dp4.2_recycle10</t>
+          <t>catalyst_repl_95.24EURkg_1y</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2333687232337815</v>
+        <v>0.0360827531009113</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{"cat_term": [95.24, 1.0]}</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1475,20 +1589,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>combined_primary_cat4y_dp4.2_recycle10</t>
+          <t>combined_primary_cat1y_dp4.2_recycle10</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1966449733212746</v>
+        <v>0.214337388670831</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{"cat_term": [95.24, 1.0], "loop_dp": 4.2, "recycle_mult": 10.0}</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1497,20 +1616,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>recycle_weight_nyari</t>
+          <t>catalyst_repl_95.24EURkg_4y</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2231532873259957</v>
+        <v>0.01507943393823929</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>{"cat_term": [95.24, 4.0]}</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1519,20 +1643,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_1y</t>
+          <t>combined_cat3y_dp3.75_h2half</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3376088702102948</v>
+        <v>0.02546028631098999</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>{"cat_term": [18.1, 3.0], "loop_dp": 3.75, "h2_price": 1548.7}</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1541,20 +1670,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75_recycle2.68</t>
+          <t>catalyst_repl_18.1EURkg_3y</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2868523498031414</v>
+        <v>0.03004596571452928</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>{"cat_term": [18.1, 3.0]}</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1563,20 +1697,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75_h2half</t>
+          <t>catalyst_repl_18.1EURkg_5y</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E9" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3052838843237611</v>
+        <v>0.03296157019915648</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>{"cat_term": [18.1, 5.0]}</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1585,20 +1724,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>catalyst_repl_18.1EURkg_3y</t>
+          <t>h2_price_half</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3562480953799437</v>
+        <v>0.03229224411881603</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>{"h2_price": 1548.7}</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1607,20 +1751,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>catalyst_repl_18.1EURkg_5y</t>
+          <t>catalyst_repl_95.24EURkg_6y</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3571340601230061</v>
+        <v>0.01858847257155776</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{"cat_term": [95.24, 6.0]}</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1629,20 +1778,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>h2_price_half</t>
+          <t>combined_primary_cat4y_dp4.2_recycle10</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E12" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3312334155723725</v>
+        <v>0.05043011383046572</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{"cat_term": [95.24, 4.0], "loop_dp": 4.2, "recycle_mult": 10.0}</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1651,20 +1805,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>perez_fortes_prices</t>
+          <t>combined_cat3y_dp3.75</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3498473699884074</v>
+        <v>0.03064665922436082</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>{"cat_term": [18.1, 3.0], "loop_dp": 3.75}</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1673,20 +1832,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>recycle_flow_x2.68</t>
+          <t>combined_cat3y_dp3.75_recycle2.68</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3270474900765253</v>
+        <v>0.0354688032319774</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{"cat_term": [18.1, 3.0], "loop_dp": 3.75, "recycle_mult": 2.68}</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1695,20 +1859,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_4y</t>
+          <t>pf_aligned_capital</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3500709824471828</v>
+        <v>0.03527097338419925</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{"capex_mult": 1.5089145254326166}</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1717,20 +1886,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_6y</t>
+          <t>pf_aligned_recycle_compression_capital</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3541493836095832</v>
+        <v>0.03509866930518098</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{"recycle_mult": 0.8736221862859904, "elec_price": 129.05500705218617, "capex_mult": 1.5089145254326166}</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1739,20 +1913,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>loop_dp_4.2bar</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E17" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3303256739439167</v>
+        <v>0.03543670955907956</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1761,20 +1940,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75</t>
+          <t>loop_dp_3.75bar</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E18" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3333426344061412</v>
+        <v>0.03607271308302311</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{"loop_dp": 3.75}</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1783,20 +1967,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>perez_fortes_prices</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3583691520442965</v>
+        <v>0.03547803225985205</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{"h2_price": 3090.0, "co2_price": 0.0, "elec_price": 95.1}</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1805,20 +1994,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>loop_dp_3.75bar</t>
+          <t>recycle_flow_x2.68</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3280425677479598</v>
+        <v>0.03997556478967655</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>{"recycle_mult": 2.68}</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1827,20 +2021,189 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>loop_dp_4.2bar</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="n">
+        <v>40</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.03619719839991829</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>{"loop_dp": 4.2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>ec_split_campos_SI</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>54</v>
-      </c>
-      <c r="D21" t="n">
-        <v>82</v>
-      </c>
-      <c r="E21" t="n">
-        <v>37</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.3565569267074893</v>
+      <c r="C22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" t="n">
+        <v>40</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.03588422420700085</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>{"ec_ref": {"Reactor modules": 32.18, "Carbon dioxide compressor": 27.1, "Hydrogen compressor": 10.02, "Recycle/reflux compressor": 0.52, "Reactor preheaters": 3.0023999999999997, "Heat exchangers": 2.5576, "Flash drums": 0.18, "Distillation column": 2.99, "Pump": 0.11, "Furnace &amp; blower": 4.1, "Turbine &amp; generator": 2.75}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pf_aligned_recycle</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15</v>
+      </c>
+      <c r="D23" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.03500540776512195</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>{"recycle_mult": 0.8736221862859904}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pf_aligned_compression</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>40</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.03562177433717181</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>{"elec_price": 129.05500705218617}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>recycle_weight_nyari</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" t="n">
+        <v>40</v>
+      </c>
+      <c r="E25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.06925827759070129</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>{"loop_dp": 4.2, "recycle_mult": 10.0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>constants drawn on panel d</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>source: analysis/meoh_plant_benchmark_2026_10_06/sensitivity_summary.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>pf_alignment.recycle_mult</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.8736221862859904</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>pf_alignment.elec_mult</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1.433944522802069</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pf_alignment.capex_mult</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1.508914525432617</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig4.xlsx
+++ b/source_data/SourceData_EDFig4.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>analysis/meoh_plant_benchmark_2026_10_06/sensitivity_summary.json (variants)</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/plant_variants/sensitivity_summary.json (variants)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>analysis/meoh_plant_benchmark_2026_10_06/sensitivity_summary.json</t>
+          <t>analysis/meoh_field_pooled_2026_10_15/robustness/plant_variants/sensitivity_summary.json</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1515,7 +1515,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_plant_benchmark_2026_10_06/sensitivity_summary.json (variants)</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/plant_variants/sensitivity_summary.json (variants)</t>
         </is>
       </c>
     </row>
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0360827531009113</v>
+        <v>0.03244056693320593</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1593,16 +1593,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>0.214337388670831</v>
+        <v>0.06792229629237283</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1620,13 +1620,13 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" t="n">
+        <v>81</v>
+      </c>
+      <c r="E6" t="n">
         <v>13</v>
-      </c>
-      <c r="D6" t="n">
-        <v>40</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>0.01507943393823929</v>
@@ -1643,24 +1643,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>combined_cat3y_dp3.75_h2half</t>
+          <t>combined_primary_cat4y_dp4.2_recycle10</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02546028631098999</v>
+        <v>0.0590481558615326</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{"cat_term": [18.1, 3.0], "loop_dp": 3.75, "h2_price": 1548.7}</t>
+          <t>{"cat_term": [95.24, 4.0], "loop_dp": 4.2, "recycle_mult": 10.0}</t>
         </is>
       </c>
     </row>
@@ -1670,24 +1670,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>catalyst_repl_18.1EURkg_3y</t>
+          <t>combined_cat3y_dp3.75_h2half</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03004596571452928</v>
+        <v>0.02546028631098999</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>{"cat_term": [18.1, 3.0]}</t>
+          <t>{"cat_term": [18.1, 3.0], "loop_dp": 3.75, "h2_price": 1548.7}</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1697,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>catalyst_repl_18.1EURkg_5y</t>
+          <t>catalyst_repl_18.1EURkg_3y</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" t="n">
+        <v>81</v>
+      </c>
+      <c r="E9" t="n">
         <v>14</v>
       </c>
-      <c r="D9" t="n">
-        <v>40</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8</v>
-      </c>
       <c r="F9" t="n">
-        <v>0.03296157019915648</v>
+        <v>0.03004596571452928</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>{"cat_term": [18.1, 5.0]}</t>
+          <t>{"cat_term": [18.1, 3.0]}</t>
         </is>
       </c>
     </row>
@@ -1724,24 +1724,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>h2_price_half</t>
+          <t>catalyst_repl_18.1EURkg_5y</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>81</v>
+      </c>
+      <c r="E10" t="n">
         <v>14</v>
       </c>
-      <c r="D10" t="n">
-        <v>40</v>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
       <c r="F10" t="n">
-        <v>0.03229224411881603</v>
+        <v>0.03287708685126324</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{"h2_price": 1548.7}</t>
+          <t>{"cat_term": [18.1, 5.0]}</t>
         </is>
       </c>
     </row>
@@ -1751,24 +1751,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>catalyst_repl_95.24EURkg_6y</t>
+          <t>h2_price_half</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D11" t="n">
+        <v>81</v>
+      </c>
+      <c r="E11" t="n">
         <v>14</v>
       </c>
-      <c r="D11" t="n">
-        <v>40</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
       <c r="F11" t="n">
-        <v>0.01858847257155776</v>
+        <v>0.03229224411881603</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>{"cat_term": [95.24, 6.0]}</t>
+          <t>{"h2_price": 1548.7}</t>
         </is>
       </c>
     </row>
@@ -1778,24 +1778,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>combined_primary_cat4y_dp4.2_recycle10</t>
+          <t>catalyst_repl_95.24EURkg_6y</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" t="n">
+        <v>81</v>
+      </c>
+      <c r="E12" t="n">
         <v>14</v>
       </c>
-      <c r="D12" t="n">
-        <v>40</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
-      </c>
       <c r="F12" t="n">
-        <v>0.05043011383046572</v>
+        <v>0.01885858265729159</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>{"cat_term": [95.24, 4.0], "loop_dp": 4.2, "recycle_mult": 10.0}</t>
+          <t>{"cat_term": [95.24, 6.0]}</t>
         </is>
       </c>
     </row>
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="n">
+        <v>81</v>
+      </c>
+      <c r="E13" t="n">
         <v>14</v>
-      </c>
-      <c r="D13" t="n">
-        <v>40</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
       </c>
       <c r="F13" t="n">
         <v>0.03064665922436082</v>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="n">
+        <v>81</v>
+      </c>
+      <c r="E14" t="n">
         <v>14</v>
-      </c>
-      <c r="D14" t="n">
-        <v>40</v>
-      </c>
-      <c r="E14" t="n">
-        <v>8</v>
       </c>
       <c r="F14" t="n">
         <v>0.0354688032319774</v>
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" t="n">
+        <v>81</v>
+      </c>
+      <c r="E15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>40</v>
-      </c>
-      <c r="E15" t="n">
-        <v>8</v>
-      </c>
       <c r="F15" t="n">
-        <v>0.03527097338419925</v>
+        <v>0.03396466223817685</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1890,16 +1890,16 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" t="n">
+        <v>81</v>
+      </c>
+      <c r="E16" t="n">
         <v>14</v>
       </c>
-      <c r="D16" t="n">
-        <v>40</v>
-      </c>
-      <c r="E16" t="n">
-        <v>8</v>
-      </c>
       <c r="F16" t="n">
-        <v>0.03509866930518098</v>
+        <v>0.03422994941367447</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" t="n">
+        <v>81</v>
+      </c>
+      <c r="E17" t="n">
         <v>15</v>
-      </c>
-      <c r="D17" t="n">
-        <v>40</v>
-      </c>
-      <c r="E17" t="n">
-        <v>9</v>
       </c>
       <c r="F17" t="n">
         <v>0.03543670955907956</v>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" t="n">
+        <v>81</v>
+      </c>
+      <c r="E18" t="n">
         <v>15</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40</v>
-      </c>
-      <c r="E18" t="n">
-        <v>9</v>
       </c>
       <c r="F18" t="n">
         <v>0.03607271308302311</v>
@@ -1971,16 +1971,16 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" t="n">
+        <v>81</v>
+      </c>
+      <c r="E19" t="n">
         <v>15</v>
       </c>
-      <c r="D19" t="n">
-        <v>40</v>
-      </c>
-      <c r="E19" t="n">
-        <v>9</v>
-      </c>
       <c r="F19" t="n">
-        <v>0.03547803225985205</v>
+        <v>0.03300359726200394</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1998,13 +1998,13 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" t="n">
+        <v>81</v>
+      </c>
+      <c r="E20" t="n">
         <v>15</v>
-      </c>
-      <c r="D20" t="n">
-        <v>40</v>
-      </c>
-      <c r="E20" t="n">
-        <v>9</v>
       </c>
       <c r="F20" t="n">
         <v>0.03997556478967655</v>
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" t="n">
+        <v>81</v>
+      </c>
+      <c r="E21" t="n">
         <v>15</v>
-      </c>
-      <c r="D21" t="n">
-        <v>40</v>
-      </c>
-      <c r="E21" t="n">
-        <v>9</v>
       </c>
       <c r="F21" t="n">
         <v>0.03619719839991829</v>
@@ -2052,13 +2052,13 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>25</v>
+      </c>
+      <c r="D22" t="n">
+        <v>81</v>
+      </c>
+      <c r="E22" t="n">
         <v>15</v>
-      </c>
-      <c r="D22" t="n">
-        <v>40</v>
-      </c>
-      <c r="E22" t="n">
-        <v>9</v>
       </c>
       <c r="F22" t="n">
         <v>0.03588422420700085</v>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>81</v>
+      </c>
+      <c r="E23" t="n">
         <v>15</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40</v>
-      </c>
-      <c r="E23" t="n">
-        <v>9</v>
       </c>
       <c r="F23" t="n">
         <v>0.03500540776512195</v>
@@ -2106,13 +2106,13 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" t="n">
+        <v>81</v>
+      </c>
+      <c r="E24" t="n">
         <v>15</v>
-      </c>
-      <c r="D24" t="n">
-        <v>40</v>
-      </c>
-      <c r="E24" t="n">
-        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>0.03562177433717181</v>
@@ -2133,16 +2133,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D25" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="E25" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>0.06925827759070129</v>
+        <v>0.06106596921395406</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>source: analysis/meoh_plant_benchmark_2026_10_06/sensitivity_summary.json</t>
+          <t>source: analysis/meoh_field_pooled_2026_10_15/robustness/plant_variants/sensitivity_summary.json</t>
         </is>
       </c>
     </row>
